--- a/xlsx/敌人怪物/进攻怪.xlsx
+++ b/xlsx/敌人怪物/进攻怪.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12200" firstSheet="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="进攻怪演员.ts" sheetId="4" r:id="rId1"/>
@@ -193,7 +193,7 @@
     <t>进攻怪</t>
   </si>
   <si>
-    <t>hfoo</t>
+    <t>近战单位</t>
   </si>
   <si>
     <t>感染者</t>
@@ -1549,25 +1549,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="25.4272727272727" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6818181818182" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.2090909090909" style="1" customWidth="1"/>
-    <col min="4" max="4" width="12.9454545454545" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.0545454545455" style="1" customWidth="1"/>
-    <col min="6" max="6" width="35.6454545454545" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.2272727272727" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.2272727272727" customWidth="1"/>
-    <col min="11" max="11" width="14.6727272727273" customWidth="1"/>
-    <col min="12" max="18" width="9.76363636363636" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.2727272727273" style="1" customWidth="1"/>
-    <col min="20" max="20" width="27.0181818181818" style="1" customWidth="1"/>
-    <col min="21" max="22" width="9.76363636363636" style="1" customWidth="1"/>
-    <col min="23" max="23" width="16.7272727272727" style="1" customWidth="1"/>
-    <col min="24" max="24" width="32.6545454545455" style="1" customWidth="1"/>
-    <col min="25" max="16382" width="9.76363636363636" style="1" customWidth="1"/>
-    <col min="16383" max="16383" width="9.76363636363636" style="1"/>
+    <col min="1" max="1" width="25.425" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.2083333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.9416666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.0583333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.6416666666667" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.225" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11.225" customWidth="1"/>
+    <col min="11" max="11" width="14.675" customWidth="1"/>
+    <col min="12" max="18" width="9.76666666666667" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.275" style="1" customWidth="1"/>
+    <col min="20" max="20" width="27.0166666666667" style="1" customWidth="1"/>
+    <col min="21" max="22" width="9.76666666666667" style="1" customWidth="1"/>
+    <col min="23" max="23" width="16.725" style="1" customWidth="1"/>
+    <col min="24" max="24" width="32.6583333333333" style="1" customWidth="1"/>
+    <col min="25" max="16382" width="9.76666666666667" style="1" customWidth="1"/>
+    <col min="16383" max="16383" width="9.76666666666667" style="1"/>
     <col min="16384" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
